--- a/temp/assessment_outputs/genie_scorecard_brz_dev.xlsx
+++ b/temp/assessment_outputs/genie_scorecard_brz_dev.xlsx
@@ -1042,7 +1042,7 @@
       <c r="C27" s="12" t="inlineStr"/>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>El número de órdenes por segmento de mercado varía según los datos. Por ejemplo, el segmento 'AUTOMOBILE' podría tener 29,000 órdenes, 'BUILDING' 27,500, 'FURNITURE' 28,000, 'HOUSEHOLD' 28,500 y 'MACHINERY' 27,000 (valores hipotéticos ilustrativos). La consulta SQL proporcionada calculará los valores reales.</t>
+          <t>El número de órdenes por segmento de mercado varía según los datos. Por ejemplo, el segmento 'AUTOMOBILE' podría tener 29,752 órdenes, 'BUILDING' 27,631, 'FURNITURE' 28,144, 'HOUSEHOLD' 28,823 y 'MACHINERY' 27,650 (valores hipotéticos ilustrativos). La consulta SQL proporcionada calculará los valores reales.</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr"/>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="H27" s="12" t="inlineStr">
         <is>
-          <t>La pregunta solicita el conteo de órdenes agrupadas por segmento de mercado. La tabla fact_sales_demo_genie contiene el campo order_id (que puede repetirse por línea de producto) y customer_id. La tabla dim_customer_demo_genie contiene el campo market_segment y customer_id como llave primaria. Uniendo ambas tablas por customer_id y usando COUNT(DISTINCT order_id) se obtiene el número único de órdenes por segmento. No hay ambigüedad en la pregunta ni datos faltantes.</t>
+          <t>La pregunta solicita el conteo de órdenes agrupadas por segmento de mercado. La tabla de hechos 'fact_sales_demo_genie' contiene el campo 'order_id' (identificador de orden) y 'customer_id' (para enlazar con el cliente). La dimensión 'dim_customer_demo_genie' contiene el campo 'market_segment'. Mediante un JOIN entre ambas tablas por 'customer_id' y usando COUNT(DISTINCT order_id) agrupado por 'market_segment', se puede responder la pregunta de forma completa y precisa. No hay ambigüedad ni datos faltantes.</t>
         </is>
       </c>
       <c r="I27" s="12" t="inlineStr">
